--- a/data/trans_orig/P57B4_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P57B4_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha tenido la sensación de disfrutar de la vida en 2023</t>
+          <t>Población según si ha tenido la sensación de disfrutar de la vida en 2023 (tasa de respuesta: 99,21%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>227960</t>
+          <t>233180</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>296813</t>
+          <t>297833</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>74,24%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>153495</t>
+          <t>151252</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>200953</t>
+          <t>199385</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>63,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>397147</t>
+          <t>401259</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>483686</t>
+          <t>482623</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>67,69%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76829</t>
+          <t>76736</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>142495</t>
+          <t>139524</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>86492</t>
+          <t>86912</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>133399</t>
+          <t>132957</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>176788</t>
+          <t>179637</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>259039</t>
+          <t>258071</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,19%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13816</t>
+          <t>14234</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>47771</t>
+          <t>48749</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13842</t>
+          <t>13615</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39325</t>
+          <t>40353</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>33617</t>
+          <t>32331</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>76001</t>
+          <t>72133</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -1069,97 +1069,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>3344</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4459</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>10459</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>3,34%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>3344</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>11671</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>11557</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>3,73%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>3344</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>11991</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>180113</t>
+          <t>180660</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>234693</t>
+          <t>233990</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>131503</t>
+          <t>135760</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>255800</t>
+          <t>252219</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>49,56%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>314319</t>
+          <t>306157</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>465208</t>
+          <t>467521</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>50,23%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>151562</t>
+          <t>150829</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>203180</t>
+          <t>202381</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>197446</t>
+          <t>200204</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>350412</t>
+          <t>344806</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>371774</t>
+          <t>372023</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>541796</t>
+          <t>552145</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>59,32%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18057</t>
+          <t>19338</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>46252</t>
+          <t>46226</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21380</t>
+          <t>21573</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>49940</t>
+          <t>51250</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>47638</t>
+          <t>48248</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>88507</t>
+          <t>88050</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3589</t>
+          <t>3849</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16776</t>
+          <t>17450</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5446</t>
+          <t>5757</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21191</t>
+          <t>21963</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>11260</t>
+          <t>12394</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>31821</t>
+          <t>31670</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>252072</t>
+          <t>252095</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>301381</t>
+          <t>299823</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>225800</t>
+          <t>223729</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>263521</t>
+          <t>263710</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>489949</t>
+          <t>487526</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>552545</t>
+          <t>549925</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>45,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>51,04%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>171600</t>
+          <t>173342</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>218925</t>
+          <t>219056</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>213397</t>
+          <t>213638</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>251331</t>
+          <t>251215</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>399926</t>
+          <t>401002</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>460859</t>
+          <t>459955</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>42,69%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37179</t>
+          <t>36972</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>62616</t>
+          <t>64111</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>41216</t>
+          <t>40491</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62691</t>
+          <t>62515</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>82493</t>
+          <t>83806</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>117091</t>
+          <t>118824</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,03%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8019</t>
+          <t>7701</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24097</t>
+          <t>23779</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8624</t>
+          <t>8676</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21471</t>
+          <t>20899</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19454</t>
+          <t>19302</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>40308</t>
+          <t>40622</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>332150</t>
+          <t>332645</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>699923</t>
+          <t>707502</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>188676</t>
+          <t>186198</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>243208</t>
+          <t>244614</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>547574</t>
+          <t>544963</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1070190</t>
+          <t>1084608</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>68,15%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>132972</t>
+          <t>122231</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>410583</t>
+          <t>407554</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>331719</t>
+          <t>333032</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>411590</t>
+          <t>415537</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>58,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>391198</t>
+          <t>363797</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>780633</t>
+          <t>777151</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>48,83%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>34993</t>
+          <t>37151</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>118086</t>
+          <t>119667</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>83834</t>
+          <t>84596</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>123517</t>
+          <t>121806</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>110381</t>
+          <t>108929</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>225287</t>
+          <t>225059</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,14%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9376</t>
+          <t>9134</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>58309</t>
+          <t>56509</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16323</t>
+          <t>16215</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31355</t>
+          <t>32244</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>27703</t>
+          <t>28387</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>76563</t>
+          <t>77216</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>170815</t>
+          <t>171585</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>213413</t>
+          <t>214822</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>141603</t>
+          <t>138649</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>172231</t>
+          <t>171164</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>320586</t>
+          <t>323893</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>375218</t>
+          <t>375311</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,11%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>244504</t>
+          <t>244625</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>289295</t>
+          <t>288520</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>237295</t>
+          <t>237717</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>271612</t>
+          <t>272729</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>493892</t>
+          <t>493047</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>551414</t>
+          <t>549315</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>49,92%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>68645</t>
+          <t>69027</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>99355</t>
+          <t>99851</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>96233</t>
+          <t>96737</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>122359</t>
+          <t>124597</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>173951</t>
+          <t>174796</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>215930</t>
+          <t>214369</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,48%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>8892</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>23743</t>
+          <t>23066</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>15632</t>
+          <t>14677</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>28663</t>
+          <t>28472</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>27273</t>
+          <t>27728</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>46647</t>
+          <t>47345</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>109031</t>
+          <t>108117</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>139296</t>
+          <t>138149</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,17 +3605,17 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>319262</t>
+          <t>319263</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>165308</t>
+          <t>166836</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>480158</t>
+          <t>488066</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>294493</t>
+          <t>292278</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>720634</t>
+          <t>682207</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>70,18%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>159411</t>
+          <t>158340</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>189635</t>
+          <t>189274</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>84576</t>
+          <t>83670</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>310491</t>
+          <t>310201</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>176062</t>
+          <t>203554</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>485017</t>
+          <t>486207</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>50,02%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>48821</t>
+          <t>49786</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>71357</t>
+          <t>71521</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>32388</t>
+          <t>28722</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>116801</t>
+          <t>116027</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>66336</t>
+          <t>70001</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>175587</t>
+          <t>176120</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,12%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5037</t>
+          <t>5113</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>14773</t>
+          <t>14814</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>4393</t>
+          <t>3313</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>21145</t>
+          <t>20566</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>9287</t>
+          <t>9210</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>30253</t>
+          <t>30283</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>605473</t>
+          <t>605474</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>605473</t>
+          <t>605474</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>605473</t>
+          <t>605474</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>57605</t>
+          <t>55450</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>79322</t>
+          <t>79258</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>52990</t>
+          <t>52312</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>73079</t>
+          <t>72883</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>114910</t>
+          <t>115373</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>146966</t>
+          <t>146173</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,08%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>134395</t>
+          <t>135590</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>160835</t>
+          <t>161971</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>48,72%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>203836</t>
+          <t>205530</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>232743</t>
+          <t>233243</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>56,19%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>345373</t>
+          <t>345032</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>384740</t>
+          <t>384651</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>55,48%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>45685</t>
+          <t>45565</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>65784</t>
+          <t>65979</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>100982</t>
+          <t>100097</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>125838</t>
+          <t>124725</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>152917</t>
+          <t>151751</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>184559</t>
+          <t>184618</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,63%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>4455</t>
+          <t>4250</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>13071</t>
+          <t>12890</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>15293</t>
+          <t>15016</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>28528</t>
+          <t>27528</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>21715</t>
+          <t>22306</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>36864</t>
+          <t>37011</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>1468868</t>
+          <t>1460564</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2056842</t>
+          <t>1982501</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>1228477</t>
+          <t>1228341</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>1847207</t>
+          <t>1774694</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>2753967</t>
+          <t>2735154</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>3622464</t>
+          <t>3545440</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>50,09%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1029513</t>
+          <t>1090708</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1477263</t>
+          <t>1486636</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1315468</t>
+          <t>1338771</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1766227</t>
+          <t>1768763</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2545387</t>
+          <t>2601003</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>3189077</t>
+          <t>3199985</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>45,21%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>296750</t>
+          <t>304242</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>432869</t>
+          <t>431791</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>413900</t>
+          <t>422031</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>562106</t>
+          <t>563810</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>766629</t>
+          <t>773080</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>964875</t>
+          <t>972187</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,73%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>57405</t>
+          <t>57652</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>108991</t>
+          <t>109672</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>85539</t>
+          <t>85084</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>125495</t>
+          <t>127549</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>153767</t>
+          <t>155875</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>218549</t>
+          <t>224266</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57B4_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P57B4_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>266285</t>
+          <t>266696</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>233180</t>
+          <t>234468</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>297833</t>
+          <t>293925</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>66,14%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>72,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>176574</t>
+          <t>201187</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>151252</t>
+          <t>172517</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>199385</t>
+          <t>226444</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>442859</t>
+          <t>467883</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>401259</t>
+          <t>426635</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>482623</t>
+          <t>506719</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>61,1%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>55,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>66,17%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>106834</t>
+          <t>110049</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76736</t>
+          <t>84842</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>139524</t>
+          <t>142358</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,27 +873,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>109744</t>
+          <t>126261</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>86912</t>
+          <t>103755</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>132957</t>
+          <t>153889</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>216578</t>
+          <t>236310</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>179637</t>
+          <t>200977</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>258071</t>
+          <t>278190</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>36,33%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>26702</t>
+          <t>26469</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14234</t>
+          <t>14264</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>48749</t>
+          <t>44633</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>23538</t>
+          <t>31665</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13615</t>
+          <t>19018</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>40353</t>
+          <t>49535</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>50239</t>
+          <t>58134</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>32331</t>
+          <t>38935</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>72133</t>
+          <t>82069</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,72%</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3344</t>
+          <t>3399</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10459</t>
+          <t>11731</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>3344</t>
+          <t>3399</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11557</t>
+          <t>12022</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>399820</t>
+          <t>403214</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>399820</t>
+          <t>403214</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>399820</t>
+          <t>403214</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>713020</t>
+          <t>765726</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>713020</t>
+          <t>765726</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>713020</t>
+          <t>765726</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>206700</t>
+          <t>228998</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>180660</t>
+          <t>199474</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>233990</t>
+          <t>259801</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>54,65%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>211550</t>
+          <t>233189</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>135760</t>
+          <t>209050</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>252219</t>
+          <t>255710</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>418250</t>
+          <t>462188</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>306157</t>
+          <t>428426</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>467521</t>
+          <t>504984</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>51,89%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>176176</t>
+          <t>203361</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>150829</t>
+          <t>172955</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>202381</t>
+          <t>233092</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>249327</t>
+          <t>207099</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>200204</t>
+          <t>183185</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>344806</t>
+          <t>230672</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>41,6%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>425503</t>
+          <t>410460</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>372023</t>
+          <t>373385</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>552145</t>
+          <t>447297</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>45,96%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>30237</t>
+          <t>33577</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19338</t>
+          <t>22010</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>46226</t>
+          <t>50700</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>36076</t>
+          <t>44653</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21573</t>
+          <t>32936</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51250</t>
+          <t>58450</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>66313</t>
+          <t>78230</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>48248</t>
+          <t>60623</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>88050</t>
+          <t>99291</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>10,2%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8770</t>
+          <t>9460</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3849</t>
+          <t>3884</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17450</t>
+          <t>17873</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11926</t>
+          <t>12850</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5757</t>
+          <t>6984</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21963</t>
+          <t>22141</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>20695</t>
+          <t>22310</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>12394</t>
+          <t>14125</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>31670</t>
+          <t>34095</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>421882</t>
+          <t>475397</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>421882</t>
+          <t>475397</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>421882</t>
+          <t>475397</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>508879</t>
+          <t>497791</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>508879</t>
+          <t>497791</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>508879</t>
+          <t>497791</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>930761</t>
+          <t>973188</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>930761</t>
+          <t>973188</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>930761</t>
+          <t>973188</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>275360</t>
+          <t>308268</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>252095</t>
+          <t>282377</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>299823</t>
+          <t>335980</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>244087</t>
+          <t>276114</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>223729</t>
+          <t>255936</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>263710</t>
+          <t>297859</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>47,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>519446</t>
+          <t>584382</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>487526</t>
+          <t>547531</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>549925</t>
+          <t>618533</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>44,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>49,81%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>197079</t>
+          <t>230893</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>173342</t>
+          <t>204427</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>219056</t>
+          <t>256889</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>233292</t>
+          <t>270239</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>213638</t>
+          <t>250238</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>251215</t>
+          <t>290996</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>430370</t>
+          <t>501132</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>401002</t>
+          <t>469034</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>459955</t>
+          <t>536038</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>43,16%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>48565</t>
+          <t>61851</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36972</t>
+          <t>47176</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>64111</t>
+          <t>78006</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>50893</t>
+          <t>59481</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40491</t>
+          <t>48670</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62515</t>
+          <t>71611</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>99458</t>
+          <t>121332</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>83806</t>
+          <t>103764</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>118824</t>
+          <t>141993</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,43%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14053</t>
+          <t>18747</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7701</t>
+          <t>11300</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23779</t>
+          <t>30537</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,17 +2237,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14197</t>
+          <t>16305</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8676</t>
+          <t>10275</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20899</t>
+          <t>23542</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,47 +2257,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
+          <t>3,78%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>35052</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>23856</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>47824</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>2,82%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>3,85%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>28249</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>19302</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>40622</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>2,62%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>535057</t>
+          <t>619758</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>535057</t>
+          <t>619758</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>535057</t>
+          <t>619758</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1077524</t>
+          <t>1241898</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1077524</t>
+          <t>1241898</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1077524</t>
+          <t>1241898</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>495084</t>
+          <t>281793</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>332645</t>
+          <t>256264</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>707502</t>
+          <t>309688</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>221411</t>
+          <t>245582</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>186198</t>
+          <t>225263</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>244614</t>
+          <t>267515</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>716495</t>
+          <t>527375</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>544963</t>
+          <t>494958</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1084608</t>
+          <t>558489</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>39,11%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>286091</t>
+          <t>310363</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>122231</t>
+          <t>284264</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>407554</t>
+          <t>335474</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>44,49%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>359261</t>
+          <t>354843</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>333032</t>
+          <t>334969</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>415537</t>
+          <t>376249</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>645353</t>
+          <t>665205</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>363797</t>
+          <t>633866</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>777151</t>
+          <t>701208</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>49,11%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>80089</t>
+          <t>89140</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>37151</t>
+          <t>72727</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>119667</t>
+          <t>109309</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>102559</t>
+          <t>104978</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>84596</t>
+          <t>90994</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>121806</t>
+          <t>119904</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>182648</t>
+          <t>194117</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>108929</t>
+          <t>173820</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>225059</t>
+          <t>220414</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>15,44%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>23778</t>
+          <t>16245</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9134</t>
+          <t>10010</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>56509</t>
+          <t>26019</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>23288</t>
+          <t>24943</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16215</t>
+          <t>18447</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32244</t>
+          <t>34746</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>47066</t>
+          <t>41188</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28387</t>
+          <t>31655</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>77216</t>
+          <t>53048</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>885043</t>
+          <t>697541</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>885043</t>
+          <t>697541</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>885043</t>
+          <t>697541</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>706519</t>
+          <t>730346</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>706519</t>
+          <t>730346</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>706519</t>
+          <t>730346</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1591562</t>
+          <t>1427886</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1591562</t>
+          <t>1427886</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1591562</t>
+          <t>1427886</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>192290</t>
+          <t>212723</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>171585</t>
+          <t>188693</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>214822</t>
+          <t>235724</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>156222</t>
+          <t>176871</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>138649</t>
+          <t>160756</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>171164</t>
+          <t>196138</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>348511</t>
+          <t>389594</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>323893</t>
+          <t>360938</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>375311</t>
+          <t>418891</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>34,68%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>267296</t>
+          <t>286397</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>244625</t>
+          <t>262796</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>288520</t>
+          <t>309379</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>51,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>254636</t>
+          <t>280290</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>237717</t>
+          <t>259965</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>272729</t>
+          <t>297217</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>49,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>521932</t>
+          <t>566687</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>493047</t>
+          <t>537118</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>549315</t>
+          <t>596256</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>46,91%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>49,36%</t>
         </is>
       </c>
     </row>
@@ -3227,22 +3227,22 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>83765</t>
+          <t>89976</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>69027</t>
+          <t>74968</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>99851</t>
+          <t>108141</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>109926</t>
+          <t>121270</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>96737</t>
+          <t>107005</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>124597</t>
+          <t>135702</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>193691</t>
+          <t>211246</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>174796</t>
+          <t>189396</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>214369</t>
+          <t>233907</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,36%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>14870</t>
+          <t>16829</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>10558</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>23066</t>
+          <t>26500</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>21308</t>
+          <t>23605</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>14677</t>
+          <t>16693</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>28472</t>
+          <t>33066</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>36177</t>
+          <t>40434</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>27728</t>
+          <t>30901</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>47345</t>
+          <t>51758</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>558221</t>
+          <t>605925</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>558221</t>
+          <t>605925</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>558221</t>
+          <t>605925</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>542092</t>
+          <t>602036</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>542092</t>
+          <t>602036</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>542092</t>
+          <t>602036</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1100312</t>
+          <t>1207961</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1100312</t>
+          <t>1207961</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1100312</t>
+          <t>1207961</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>124234</t>
+          <t>138758</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>108117</t>
+          <t>123834</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>138149</t>
+          <t>154761</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>319263</t>
+          <t>128203</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>166836</t>
+          <t>113370</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>488066</t>
+          <t>140610</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>443496</t>
+          <t>266961</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>292278</t>
+          <t>244154</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>682207</t>
+          <t>286967</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>34,11%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>173839</t>
+          <t>191979</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>158340</t>
+          <t>175482</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>189274</t>
+          <t>207771</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>201287</t>
+          <t>216168</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>83670</t>
+          <t>201753</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>310201</t>
+          <t>231140</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>53,02%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>375125</t>
+          <t>408148</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>203554</t>
+          <t>387030</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>486207</t>
+          <t>430789</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>51,2%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>59700</t>
+          <t>65161</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>49786</t>
+          <t>54067</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>71521</t>
+          <t>77954</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>73225</t>
+          <t>79140</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>28722</t>
+          <t>67635</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>116027</t>
+          <t>91494</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>132925</t>
+          <t>144301</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>70001</t>
+          <t>128050</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>176120</t>
+          <t>162311</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>19,29%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>8867</t>
+          <t>9483</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5113</t>
+          <t>5077</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>14814</t>
+          <t>15812</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>11699</t>
+          <t>12413</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3313</t>
+          <t>7903</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>20566</t>
+          <t>18297</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>20566</t>
+          <t>21896</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>9210</t>
+          <t>15593</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>30283</t>
+          <t>30724</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>366640</t>
+          <t>405381</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>366640</t>
+          <t>405381</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>366640</t>
+          <t>405381</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>605474</t>
+          <t>435924</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>605474</t>
+          <t>435924</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>605474</t>
+          <t>435924</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>972113</t>
+          <t>841305</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>972113</t>
+          <t>841305</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>972113</t>
+          <t>841305</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>67336</t>
+          <t>75807</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>55450</t>
+          <t>63703</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>79258</t>
+          <t>89954</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>62990</t>
+          <t>70682</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>52312</t>
+          <t>60144</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>72883</t>
+          <t>83624</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>130326</t>
+          <t>146489</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>115373</t>
+          <t>129853</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>146173</t>
+          <t>164525</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,69%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>147592</t>
+          <t>161418</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>135590</t>
+          <t>146264</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>161971</t>
+          <t>175797</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>47,88%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>218800</t>
+          <t>239013</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>205530</t>
+          <t>224465</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>233243</t>
+          <t>253742</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>366392</t>
+          <t>400430</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>345032</t>
+          <t>379816</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>384651</t>
+          <t>419921</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>52,78%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>55,35%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>55720</t>
+          <t>59981</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>45565</t>
+          <t>49522</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>65979</t>
+          <t>72112</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>112434</t>
+          <t>121332</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>100097</t>
+          <t>108911</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>124725</t>
+          <t>136554</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>168155</t>
+          <t>181313</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>151751</t>
+          <t>164161</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>184618</t>
+          <t>199424</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,29%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>7629</t>
+          <t>8255</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>4250</t>
+          <t>4568</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>12890</t>
+          <t>13695</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>20856</t>
+          <t>22172</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>15016</t>
+          <t>16043</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>27528</t>
+          <t>29573</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>28485</t>
+          <t>30426</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>22306</t>
+          <t>23268</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>37011</t>
+          <t>39398</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>278277</t>
+          <t>305461</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>278277</t>
+          <t>305461</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>278277</t>
+          <t>305461</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>415081</t>
+          <t>453199</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>415081</t>
+          <t>453199</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>415081</t>
+          <t>453199</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>693358</t>
+          <t>758659</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>693358</t>
+          <t>758659</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>693358</t>
+          <t>758659</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>1627288</t>
+          <t>1513044</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>1460564</t>
+          <t>1446631</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>1982501</t>
+          <t>1583281</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>1392096</t>
+          <t>1331827</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>1228341</t>
+          <t>1278789</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>1774694</t>
+          <t>1383064</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>3019384</t>
+          <t>2844872</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>2735154</t>
+          <t>2763340</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>3545440</t>
+          <t>2936468</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>40,69%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>1354907</t>
+          <t>1494460</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1090708</t>
+          <t>1428390</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1486636</t>
+          <t>1556661</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>1626348</t>
+          <t>1693913</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1338771</t>
+          <t>1641064</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1768763</t>
+          <t>1742774</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>2981254</t>
+          <t>3188373</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2601003</t>
+          <t>3100265</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>3199985</t>
+          <t>3268935</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>45,3%</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>384778</t>
+          <t>426154</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>304242</t>
+          <t>386282</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>431791</t>
+          <t>465187</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>508651</t>
+          <t>562520</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>422031</t>
+          <t>526464</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>563810</t>
+          <t>597818</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>893429</t>
+          <t>988673</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>773080</t>
+          <t>931602</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>972187</t>
+          <t>1042631</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>14,45%</t>
         </is>
       </c>
     </row>
@@ -5047,32 +5047,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>77966</t>
+          <t>79019</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>57652</t>
+          <t>62133</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>109672</t>
+          <t>97436</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5082,32 +5082,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>106617</t>
+          <t>115686</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>85084</t>
+          <t>97730</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>127549</t>
+          <t>132065</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>184584</t>
+          <t>194705</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>155875</t>
+          <t>173174</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>224266</t>
+          <t>222563</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>3444939</t>
+          <t>3512677</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>3444939</t>
+          <t>3512677</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3444939</t>
+          <t>3512677</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>3633712</t>
+          <t>3703946</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>3633712</t>
+          <t>3703946</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3633712</t>
+          <t>3703946</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>7078651</t>
+          <t>7216623</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>7078651</t>
+          <t>7216623</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>7078651</t>
+          <t>7216623</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
